--- a/data/file_generation/input/data_57/波兰超开赛时间_2025-10-27_03_15华沙莱吉亚__VS波兹南莱赫_比分0-0标盘明细.xlsx
+++ b/data/file_generation/input/data_57/波兰超开赛时间_2025-10-27_03_15华沙莱吉亚__VS波兹南莱赫_比分0-0标盘明细.xlsx
@@ -22504,26 +22504,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAE42E99-8CDC-41C6-A220-0E9780E3AE8A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF84B3A-38C3-486F-BB80-E00A576363B6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49B4F932-E6AF-48A3-AA51-B1935C5F9EE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AC87124-DB54-48FA-B955-EB08F0D5FF29}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD2671A5-FE66-45FF-8EDF-3DBB92770DD8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94084464-8AD2-4A65-BA19-CAFF02993327}"/>
 </file>